--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="體檢總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A級好公司" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="A級+好價格" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="循環股(看PBR)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="體檢總表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A級好公司" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A級+好價格" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="循環股(看PBR)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,142 +432,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>⑥EPS成長</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>⑧含金量</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>⑨ROE</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>②毛利位階</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>③營益位階</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>④淨利位階</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>⑤營收成長</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>①營收動能</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>⑦EPS跟上營收</t>
         </is>
@@ -21416,97 +21428,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -24513,97 +24525,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -25447,97 +25459,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>

--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="體檢總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="A級好公司" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="A級+好價格" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="循環股(看PBR)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="未來估值便宜(ForwardPE)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="體檢總表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A級好公司" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A級+好價格" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="循環股(看PBR)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未來估值便宜(ForwardPE)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,172 +433,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>⑥EPS成長</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>⑧含金量</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>⑨ROE</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>②毛利位階</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>③營益位階</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>④淨利位階</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>⑤營收成長</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>①營收動能</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>⑦EPS跟上營收</t>
         </is>
@@ -26287,127 +26299,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -30547,127 +30559,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -31830,127 +31842,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -42938,127 +42950,127 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>

--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,222 +421,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>⑥EPS成長</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>⑧含金量</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>⑨ROE</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>②毛利位階</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>③營益位階</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>④淨利位階</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>⑤營收成長</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>①營收動能</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>⑦EPS跟上營收</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
@@ -16574,7 +16562,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>💎深度買點</t>
+          <t>⚠️便宜陷阱(動態惡化)</t>
         </is>
       </c>
       <c r="AC124" t="n">
@@ -31935,172 +31923,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -37235,172 +37223,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -38745,172 +38733,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -52979,172 +52967,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>

--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,222 +421,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>⑥EPS成長</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>⑧含金量</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>⑨ROE</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>②毛利位階</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>③營益位階</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>④淨利位階</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>⑤營收成長</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>①營收動能</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>⑦EPS跟上營收</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
@@ -35387,172 +35375,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -40915,172 +40903,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -42425,172 +42413,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -58183,172 +58171,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>

--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,222 +433,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>⑥EPS成長</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>⑧含金量</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>⑨ROE</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>②毛利位階</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>③營益位階</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>④淨利位階</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>⑤營收成長</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>①營收動能</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>⑦EPS跟上營收</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>⑪動態惡化扣分</t>
         </is>
@@ -3915,12 +3927,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3932,102 +3944,84 @@
         <v>90</v>
       </c>
       <c r="E27" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>64.8</v>
       </c>
       <c r="G27" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="H27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J27" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="K27" t="n">
-        <v>206</v>
-      </c>
-      <c r="L27" t="n">
-        <v>23.7</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P27" t="n">
-        <v>8.300000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="R27" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="S27" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="T27" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>24</v>
-      </c>
-      <c r="W27" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.73</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>🟢偏便宜</t>
-        </is>
-      </c>
-      <c r="AC27" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>136.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AG27" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
         <v>12</v>
@@ -4042,10 +4036,10 @@
         <v>8</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -4447,12 +4441,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4464,84 +4458,102 @@
         <v>90</v>
       </c>
       <c r="E31" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="F31" t="n">
-        <v>64.8</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="H31" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I31" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="J31" t="n">
-        <v>61.7</v>
+        <v>41.7</v>
       </c>
       <c r="K31" t="n">
-        <v>186</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="L31" t="n">
+        <v>23.7</v>
+      </c>
       <c r="M31" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="N31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>30.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="R31" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="S31" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="T31" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>24</v>
+      </c>
+      <c r="W31" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="X31" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.73</v>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>🟢偏便宜</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>136.7</v>
+      </c>
       <c r="AF31" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
         <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>12</v>
@@ -4556,10 +4568,10 @@
         <v>8</v>
       </c>
       <c r="AO31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ31" t="n">
         <v>7</v>
@@ -34209,12 +34221,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -34224,10 +34236,10 @@
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="n">
-        <v>4</v>
+        <v>-16.6</v>
       </c>
       <c r="F264" t="n">
-        <v>37.5</v>
+        <v>4.2</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -34239,7 +34251,7 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>93.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
@@ -34251,23 +34263,23 @@
         <v>100</v>
       </c>
       <c r="P264" t="n">
-        <v>24</v>
+        <v>-4.1</v>
       </c>
       <c r="Q264" t="n">
-        <v>117.9</v>
+        <v>147.9</v>
       </c>
       <c r="R264" t="n">
-        <v>16.8</v>
+        <v>23.9</v>
       </c>
       <c r="S264" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="T264" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="V264" t="inlineStr"/>
@@ -34285,7 +34297,7 @@
       <c r="AD264" t="inlineStr"/>
       <c r="AE264" t="inlineStr"/>
       <c r="AF264" t="n">
-        <v>3.43</v>
+        <v>3.92</v>
       </c>
       <c r="AG264" t="inlineStr">
         <is>
@@ -34311,12 +34323,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -34326,10 +34338,10 @@
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="n">
-        <v>10.6</v>
+        <v>8.1</v>
       </c>
       <c r="F265" t="n">
-        <v>20.3</v>
+        <v>10.3</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -34341,7 +34353,7 @@
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>93.8</v>
+        <v>93</v>
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
@@ -34353,16 +34365,16 @@
         <v>100</v>
       </c>
       <c r="P265" t="n">
-        <v>7.1</v>
+        <v>13</v>
       </c>
       <c r="Q265" t="n">
-        <v>76.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="R265" t="n">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="S265" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T265" t="n">
         <v>100</v>
@@ -34372,14 +34384,24 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="V265" t="inlineStr"/>
-      <c r="W265" t="inlineStr"/>
-      <c r="X265" t="inlineStr"/>
-      <c r="Y265" t="inlineStr"/>
-      <c r="Z265" t="inlineStr"/>
+      <c r="V265" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X265" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>1.97</v>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr"/>
@@ -34387,13 +34409,9 @@
       <c r="AD265" t="inlineStr"/>
       <c r="AE265" t="inlineStr"/>
       <c r="AF265" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.27</v>
+      </c>
+      <c r="AG265" t="inlineStr"/>
       <c r="AH265" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34413,12 +34431,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -34428,10 +34446,10 @@
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="n">
-        <v>-1.2</v>
+        <v>-2.6</v>
       </c>
       <c r="F266" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -34443,7 +34461,7 @@
         <v>0</v>
       </c>
       <c r="J266" t="n">
-        <v>91.7</v>
+        <v>94.7</v>
       </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
@@ -34455,47 +34473,63 @@
         <v>100</v>
       </c>
       <c r="P266" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="Q266" t="n">
-        <v>227.3</v>
+        <v>17.5</v>
       </c>
       <c r="R266" t="n">
-        <v>25.1</v>
+        <v>18.5</v>
       </c>
       <c r="S266" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="T266" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr"/>
-      <c r="W266" t="inlineStr"/>
-      <c r="X266" t="inlineStr"/>
-      <c r="Y266" t="inlineStr"/>
-      <c r="Z266" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V266" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X266" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>2.36</v>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr"/>
-      <c r="AC266" t="inlineStr"/>
-      <c r="AD266" t="inlineStr"/>
-      <c r="AE266" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>🔴貴於合理價</t>
+        </is>
+      </c>
+      <c r="AC266" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>18.7</v>
+      </c>
       <c r="AF266" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>4.18</v>
+      </c>
+      <c r="AG266" t="inlineStr"/>
       <c r="AH266" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34515,12 +34549,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -34530,10 +34564,10 @@
       </c>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="n">
-        <v>-9.1</v>
+        <v>5.7</v>
       </c>
       <c r="F267" t="n">
-        <v>47.6</v>
+        <v>-0.2</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -34545,7 +34579,7 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>94.3</v>
+        <v>92</v>
       </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
@@ -34557,19 +34591,19 @@
         <v>100</v>
       </c>
       <c r="P267" t="n">
-        <v>-13.5</v>
+        <v>8</v>
       </c>
       <c r="Q267" t="n">
-        <v>28.8</v>
+        <v>22.3</v>
       </c>
       <c r="R267" t="n">
-        <v>16</v>
+        <v>19.8</v>
       </c>
       <c r="S267" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="T267" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -34586,12 +34620,22 @@
           <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
-      <c r="AB267" t="inlineStr"/>
-      <c r="AC267" t="inlineStr"/>
-      <c r="AD267" t="inlineStr"/>
-      <c r="AE267" t="inlineStr"/>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>🔴貴於合理價</t>
+        </is>
+      </c>
+      <c r="AC267" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>29.3</v>
+      </c>
       <c r="AF267" t="n">
-        <v>3.03</v>
+        <v>3.75</v>
       </c>
       <c r="AG267" t="inlineStr">
         <is>
@@ -34617,12 +34661,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -34632,10 +34676,10 @@
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="n">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="F268" t="n">
-        <v>10.3</v>
+        <v>37.5</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -34647,7 +34691,7 @@
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
@@ -34659,16 +34703,16 @@
         <v>100</v>
       </c>
       <c r="P268" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q268" t="n">
-        <v>82.7</v>
+        <v>117.9</v>
       </c>
       <c r="R268" t="n">
-        <v>20.2</v>
+        <v>16.8</v>
       </c>
       <c r="S268" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="T268" t="n">
         <v>100</v>
@@ -34678,24 +34722,14 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="V268" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W268" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X268" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Y268" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Z268" t="n">
-        <v>1.97</v>
-      </c>
+      <c r="V268" t="inlineStr"/>
+      <c r="W268" t="inlineStr"/>
+      <c r="X268" t="inlineStr"/>
+      <c r="Y268" t="inlineStr"/>
+      <c r="Z268" t="inlineStr"/>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr"/>
@@ -34703,9 +34737,13 @@
       <c r="AD268" t="inlineStr"/>
       <c r="AE268" t="inlineStr"/>
       <c r="AF268" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AG268" t="inlineStr"/>
+        <v>3.43</v>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH268" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34725,12 +34763,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -34740,10 +34778,10 @@
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="n">
-        <v>5.7</v>
+        <v>-1.2</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.2</v>
+        <v>14.5</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -34755,7 +34793,7 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>92</v>
+        <v>91.7</v>
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
@@ -34767,19 +34805,19 @@
         <v>100</v>
       </c>
       <c r="P269" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="Q269" t="n">
-        <v>22.3</v>
+        <v>227.3</v>
       </c>
       <c r="R269" t="n">
-        <v>19.8</v>
+        <v>25.1</v>
       </c>
       <c r="S269" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="T269" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -34796,22 +34834,12 @@
           <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>🔴貴於合理價</t>
-        </is>
-      </c>
-      <c r="AC269" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AD269" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AE269" t="n">
-        <v>29.3</v>
-      </c>
+      <c r="AB269" t="inlineStr"/>
+      <c r="AC269" t="inlineStr"/>
+      <c r="AD269" t="inlineStr"/>
+      <c r="AE269" t="inlineStr"/>
       <c r="AF269" t="n">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="AG269" t="inlineStr">
         <is>
@@ -34837,12 +34865,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -34852,10 +34880,10 @@
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="n">
-        <v>-2.6</v>
+        <v>-7.1</v>
       </c>
       <c r="F270" t="n">
-        <v>7.8</v>
+        <v>24.1</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -34867,7 +34895,7 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>94.7</v>
+        <v>91.2</v>
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
@@ -34879,63 +34907,47 @@
         <v>100</v>
       </c>
       <c r="P270" t="n">
-        <v>8.1</v>
+        <v>-24</v>
       </c>
       <c r="Q270" t="n">
-        <v>17.5</v>
+        <v>-172.7</v>
       </c>
       <c r="R270" t="n">
-        <v>18.5</v>
+        <v>17.4</v>
       </c>
       <c r="S270" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="T270" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V270" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W270" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X270" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Y270" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Z270" t="n">
-        <v>2.36</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr"/>
+      <c r="X270" t="inlineStr"/>
+      <c r="Y270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr"/>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>🔴貴於合理價</t>
-        </is>
-      </c>
-      <c r="AC270" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AD270" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AE270" t="n">
-        <v>18.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="inlineStr"/>
+      <c r="AD270" t="inlineStr"/>
+      <c r="AE270" t="inlineStr"/>
       <c r="AF270" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AG270" t="inlineStr"/>
+        <v>3.25</v>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH270" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34955,12 +34967,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -34970,10 +34982,10 @@
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="n">
-        <v>-16.6</v>
+        <v>-9.5</v>
       </c>
       <c r="F271" t="n">
-        <v>4.2</v>
+        <v>32.1</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -34985,7 +34997,7 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>88.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
@@ -34997,23 +35009,23 @@
         <v>100</v>
       </c>
       <c r="P271" t="n">
-        <v>-4.1</v>
+        <v>-5.9</v>
       </c>
       <c r="Q271" t="n">
-        <v>147.9</v>
+        <v>-300.3</v>
       </c>
       <c r="R271" t="n">
-        <v>23.9</v>
+        <v>16.6</v>
       </c>
       <c r="S271" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="T271" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="V271" t="inlineStr"/>
@@ -35031,7 +35043,7 @@
       <c r="AD271" t="inlineStr"/>
       <c r="AE271" t="inlineStr"/>
       <c r="AF271" t="n">
-        <v>3.92</v>
+        <v>3.08</v>
       </c>
       <c r="AG271" t="inlineStr">
         <is>
@@ -35057,12 +35069,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -35072,10 +35084,10 @@
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="n">
-        <v>8.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="F272" t="n">
-        <v>22.6</v>
+        <v>20.3</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -35087,7 +35099,7 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
@@ -35099,23 +35111,23 @@
         <v>100</v>
       </c>
       <c r="P272" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q272" t="n">
-        <v>24.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R272" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="S272" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="T272" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="V272" t="inlineStr"/>
@@ -35133,7 +35145,7 @@
       <c r="AD272" t="inlineStr"/>
       <c r="AE272" t="inlineStr"/>
       <c r="AF272" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="AG272" t="inlineStr">
         <is>
@@ -35159,12 +35171,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -35174,10 +35186,10 @@
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="n">
-        <v>-9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F273" t="n">
-        <v>32.1</v>
+        <v>22.6</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -35189,7 +35201,7 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>92.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
@@ -35201,23 +35213,23 @@
         <v>100</v>
       </c>
       <c r="P273" t="n">
-        <v>-5.9</v>
+        <v>12.2</v>
       </c>
       <c r="Q273" t="n">
-        <v>-300.3</v>
+        <v>24.8</v>
       </c>
       <c r="R273" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="S273" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="T273" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="V273" t="inlineStr"/>
@@ -35235,7 +35247,7 @@
       <c r="AD273" t="inlineStr"/>
       <c r="AE273" t="inlineStr"/>
       <c r="AF273" t="n">
-        <v>3.08</v>
+        <v>3.91</v>
       </c>
       <c r="AG273" t="inlineStr">
         <is>
@@ -35261,12 +35273,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -35276,10 +35288,10 @@
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="n">
-        <v>-7.1</v>
+        <v>-9.1</v>
       </c>
       <c r="F274" t="n">
-        <v>24.1</v>
+        <v>47.6</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -35291,7 +35303,7 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>91.2</v>
+        <v>94.3</v>
       </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
@@ -35303,16 +35315,16 @@
         <v>100</v>
       </c>
       <c r="P274" t="n">
-        <v>-24</v>
+        <v>-13.5</v>
       </c>
       <c r="Q274" t="n">
-        <v>-172.7</v>
+        <v>28.8</v>
       </c>
       <c r="R274" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="S274" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="T274" t="n">
         <v>100</v>
@@ -35337,7 +35349,7 @@
       <c r="AD274" t="inlineStr"/>
       <c r="AE274" t="inlineStr"/>
       <c r="AF274" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="AG274" t="inlineStr">
         <is>
@@ -35375,172 +35387,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -38069,12 +38081,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -38086,89 +38098,107 @@
         <v>90</v>
       </c>
       <c r="E27" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="F27" t="n">
-        <v>64.8</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="H27" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I27" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
-        <v>61.7</v>
+        <v>41.7</v>
       </c>
       <c r="K27" t="n">
-        <v>186</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.7</v>
+      </c>
       <c r="M27" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>30.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="R27" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="S27" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="T27" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.73</v>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>🟢偏便宜</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>136.7</v>
+      </c>
       <c r="AF27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -38180,96 +38210,78 @@
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>64.8</v>
       </c>
       <c r="G28" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="H28" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="I28" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J28" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="K28" t="n">
-        <v>206</v>
-      </c>
-      <c r="L28" t="n">
-        <v>23.7</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="N28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O28" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P28" t="n">
-        <v>8.300000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="R28" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="T28" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>24</v>
-      </c>
-      <c r="W28" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="X28" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.73</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>🟢偏便宜</t>
-        </is>
-      </c>
-      <c r="AC28" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>136.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AG28" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -40903,172 +40915,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -42413,172 +42425,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
@@ -53595,64 +53607,64 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E114" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="F114" t="n">
-        <v>32.7</v>
+        <v>35.8</v>
       </c>
       <c r="G114" t="n">
-        <v>14.1</v>
+        <v>24.3</v>
       </c>
       <c r="H114" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="I114" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="J114" t="n">
-        <v>58.8</v>
+        <v>56</v>
       </c>
       <c r="K114" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>1.43</v>
+        <v>-1.89</v>
       </c>
       <c r="N114" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="O114" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="P114" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>74.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="R114" t="n">
-        <v>83.40000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="S114" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T114" t="n">
         <v>99</v>
@@ -53677,14 +53689,18 @@
       <c r="AD114" t="inlineStr"/>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="n">
-        <v>0.87</v>
+        <v>1.23</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>含金量-1.9差、毛利壓歷史低檔</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -53787,64 +53803,64 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="E116" t="n">
-        <v>-34.5</v>
+        <v>18</v>
       </c>
       <c r="F116" t="n">
-        <v>-42.1</v>
+        <v>25.3</v>
       </c>
       <c r="G116" t="n">
-        <v>6.5</v>
+        <v>18.1</v>
       </c>
       <c r="H116" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="I116" t="n">
-        <v>4.9</v>
+        <v>11.1</v>
       </c>
       <c r="J116" t="n">
-        <v>24.9</v>
+        <v>38.6</v>
       </c>
       <c r="K116" t="n">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="N116" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="O116" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P116" t="n">
-        <v>-6.3</v>
+        <v>7.8</v>
       </c>
       <c r="Q116" t="n">
-        <v>35.8</v>
+        <v>17.8</v>
       </c>
       <c r="R116" t="n">
-        <v>192.6</v>
+        <v>69.5</v>
       </c>
       <c r="S116" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T116" t="n">
         <v>99</v>
@@ -53869,18 +53885,14 @@
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="n">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、ROE6低、營收5年萎縮-6%</t>
-        </is>
-      </c>
+      <c r="AH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -54481,64 +54493,64 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E123" t="n">
-        <v>18</v>
+        <v>-34.5</v>
       </c>
       <c r="F123" t="n">
-        <v>25.3</v>
+        <v>-42.1</v>
       </c>
       <c r="G123" t="n">
-        <v>18.1</v>
+        <v>6.5</v>
       </c>
       <c r="H123" t="n">
-        <v>15.7</v>
+        <v>17.4</v>
       </c>
       <c r="I123" t="n">
-        <v>11.1</v>
+        <v>4.9</v>
       </c>
       <c r="J123" t="n">
-        <v>38.6</v>
+        <v>24.9</v>
       </c>
       <c r="K123" t="n">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="N123" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O123" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="P123" t="n">
-        <v>7.8</v>
+        <v>-6.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>17.8</v>
+        <v>35.8</v>
       </c>
       <c r="R123" t="n">
-        <v>69.5</v>
+        <v>192.6</v>
       </c>
       <c r="S123" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="T123" t="n">
         <v>99</v>
@@ -54563,14 +54575,18 @@
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="n">
-        <v>0.7</v>
+        <v>0.22</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、ROE6低、營收5年萎縮-6%</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -54953,64 +54969,64 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E128" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="F128" t="n">
-        <v>35.8</v>
+        <v>32.7</v>
       </c>
       <c r="G128" t="n">
-        <v>24.3</v>
+        <v>14.1</v>
       </c>
       <c r="H128" t="n">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="I128" t="n">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="J128" t="n">
-        <v>56</v>
+        <v>58.8</v>
       </c>
       <c r="K128" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
-        <v>-1.89</v>
+        <v>1.43</v>
       </c>
       <c r="N128" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="O128" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="P128" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q128" t="n">
-        <v>64.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="R128" t="n">
-        <v>49.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="S128" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T128" t="n">
         <v>99</v>
@@ -55035,18 +55051,14 @@
       <c r="AD128" t="inlineStr"/>
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="n">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>含金量-1.9差、毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="AH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -55547,64 +55559,62 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E134" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="F134" t="n">
-        <v>12.1</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="H134" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I134" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J134" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K134" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="N134" t="n">
+        <v>77</v>
+      </c>
+      <c r="O134" t="n">
         <v>55</v>
       </c>
-      <c r="O134" t="n">
-        <v>73</v>
-      </c>
       <c r="P134" t="n">
-        <v>-5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q134" t="n">
-        <v>21.3</v>
+        <v>49.9</v>
       </c>
       <c r="R134" t="n">
-        <v>115.6</v>
+        <v>165.8</v>
       </c>
       <c r="S134" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="T134" t="n">
         <v>100</v>
@@ -55629,7 +55639,7 @@
       <c r="AD134" t="inlineStr"/>
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="n">
-        <v>0.65</v>
+        <v>0.18</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -55638,7 +55648,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-5%</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
     </row>
@@ -55939,62 +55949,64 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E138" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
+        <v>-14.6</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12.1</v>
+      </c>
       <c r="G138" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="H138" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="I138" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="J138" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K138" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
-        <v>1.73</v>
+        <v>0.99</v>
       </c>
       <c r="N138" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O138" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="P138" t="n">
-        <v>4.5</v>
+        <v>-5.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>49.9</v>
+        <v>21.3</v>
       </c>
       <c r="R138" t="n">
-        <v>165.8</v>
+        <v>115.6</v>
       </c>
       <c r="S138" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T138" t="n">
         <v>100</v>
@@ -56019,7 +56031,7 @@
       <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="n">
-        <v>0.18</v>
+        <v>0.65</v>
       </c>
       <c r="AG138" t="inlineStr">
         <is>
@@ -56028,71 +56040,71 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、營收5年萎縮-5%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E139" t="n">
-        <v>-12.8</v>
+        <v>-16.5</v>
       </c>
       <c r="F139" t="n">
-        <v>-19.8</v>
+        <v>-25.4</v>
       </c>
       <c r="G139" t="n">
-        <v>15.5</v>
+        <v>10.3</v>
       </c>
       <c r="H139" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="I139" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="J139" t="n">
-        <v>57.9</v>
+        <v>56.2</v>
       </c>
       <c r="K139" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="N139" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="O139" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P139" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q139" t="n">
-        <v>47.5</v>
+        <v>32.4</v>
       </c>
       <c r="R139" t="n">
-        <v>53.2</v>
+        <v>142.3</v>
       </c>
       <c r="S139" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="T139" t="n">
         <v>100</v>
@@ -56117,7 +56129,7 @@
       <c r="AD139" t="inlineStr"/>
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
@@ -56126,7 +56138,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️ROE滑落(10&lt;5年均16×67%)</t>
         </is>
       </c>
     </row>
@@ -56231,64 +56243,64 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E141" t="n">
-        <v>-16.5</v>
+        <v>-12.8</v>
       </c>
       <c r="F141" t="n">
-        <v>-25.4</v>
+        <v>-19.8</v>
       </c>
       <c r="G141" t="n">
-        <v>10.3</v>
+        <v>15.5</v>
       </c>
       <c r="H141" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="I141" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J141" t="n">
-        <v>56.2</v>
+        <v>57.9</v>
       </c>
       <c r="K141" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="N141" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="O141" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="P141" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q141" t="n">
-        <v>32.4</v>
+        <v>47.5</v>
       </c>
       <c r="R141" t="n">
-        <v>142.3</v>
+        <v>53.2</v>
       </c>
       <c r="S141" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T141" t="n">
         <v>100</v>
@@ -56313,7 +56325,7 @@
       <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
@@ -56322,7 +56334,7 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️ROE滑落(10&lt;5年均16×67%)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
@@ -56819,64 +56831,64 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E147" t="n">
-        <v>-5.5</v>
+        <v>0.3</v>
       </c>
       <c r="F147" t="n">
-        <v>-5.4</v>
+        <v>36.5</v>
       </c>
       <c r="G147" t="n">
-        <v>20.2</v>
+        <v>28.8</v>
       </c>
       <c r="H147" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="I147" t="n">
-        <v>11.2</v>
+        <v>17.4</v>
       </c>
       <c r="J147" t="n">
-        <v>44.6</v>
+        <v>39.7</v>
       </c>
       <c r="K147" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="N147" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O147" t="n">
+        <v>77</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="R147" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S147" t="n">
         <v>91</v>
-      </c>
-      <c r="P147" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="R147" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="S147" t="n">
-        <v>100</v>
       </c>
       <c r="T147" t="n">
         <v>100</v>
@@ -56901,7 +56913,7 @@
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
@@ -56910,71 +56922,71 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3</v>
+        <v>-5.5</v>
       </c>
       <c r="F148" t="n">
-        <v>36.5</v>
+        <v>-5.4</v>
       </c>
       <c r="G148" t="n">
-        <v>28.8</v>
+        <v>20.2</v>
       </c>
       <c r="H148" t="n">
-        <v>25.6</v>
+        <v>24.1</v>
       </c>
       <c r="I148" t="n">
-        <v>17.4</v>
+        <v>11.2</v>
       </c>
       <c r="J148" t="n">
-        <v>39.7</v>
+        <v>44.6</v>
       </c>
       <c r="K148" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
-        <v>1.21</v>
+        <v>0.92</v>
       </c>
       <c r="N148" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O148" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="P148" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q148" t="n">
-        <v>15.4</v>
+        <v>81.7</v>
       </c>
       <c r="R148" t="n">
-        <v>27.9</v>
+        <v>25.9</v>
       </c>
       <c r="S148" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="T148" t="n">
         <v>100</v>
@@ -56999,7 +57011,7 @@
       <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AG148" t="inlineStr">
         <is>
@@ -57008,71 +57020,71 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E149" t="n">
-        <v>47.6</v>
+        <v>-3.4</v>
       </c>
       <c r="F149" t="n">
-        <v>90.7</v>
+        <v>27</v>
       </c>
       <c r="G149" t="n">
-        <v>34.3</v>
+        <v>31.7</v>
       </c>
       <c r="H149" t="n">
-        <v>23</v>
+        <v>33.9</v>
       </c>
       <c r="I149" t="n">
-        <v>27.4</v>
+        <v>10</v>
       </c>
       <c r="J149" t="n">
-        <v>20.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K149" t="n">
-        <v>547</v>
+        <v>115</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="N149" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="O149" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="P149" t="n">
-        <v>28.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q149" t="n">
-        <v>172.1</v>
+        <v>21.9</v>
       </c>
       <c r="R149" t="n">
-        <v>66.5</v>
+        <v>32.2</v>
       </c>
       <c r="S149" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T149" t="n">
         <v>100</v>
@@ -57097,76 +57109,80 @@
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="n">
-        <v>0.68</v>
+        <v>2.78</v>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="E150" t="n">
-        <v>-3.4</v>
+        <v>47.6</v>
       </c>
       <c r="F150" t="n">
-        <v>27</v>
+        <v>90.7</v>
       </c>
       <c r="G150" t="n">
-        <v>31.7</v>
+        <v>34.3</v>
       </c>
       <c r="H150" t="n">
-        <v>33.9</v>
+        <v>23</v>
       </c>
       <c r="I150" t="n">
-        <v>10</v>
+        <v>27.4</v>
       </c>
       <c r="J150" t="n">
-        <v>68.40000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="K150" t="n">
-        <v>115</v>
+        <v>547</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="N150" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="O150" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="P150" t="n">
-        <v>3.8</v>
+        <v>28.8</v>
       </c>
       <c r="Q150" t="n">
-        <v>21.9</v>
+        <v>172.1</v>
       </c>
       <c r="R150" t="n">
-        <v>32.2</v>
+        <v>66.5</v>
       </c>
       <c r="S150" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T150" t="n">
         <v>100</v>
@@ -57191,18 +57207,14 @@
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="n">
-        <v>2.78</v>
+        <v>0.68</v>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="AH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -58171,172 +58183,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>代號</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>名稱</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>評等</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>品質總分</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>EPS5y%</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EPS近3y%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ROE5年均</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ROIC估算</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>負債比%</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>流動比%</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>存貨年增%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>毛利位階</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>淨利位階</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>營收5yCAGR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>月營收YoY</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>PER</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PE位階</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PBR位階</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>估值</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>成長率g%</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>預估明年EPS</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ForwardPE保守</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PEG</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>未來估值</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>鬧鐘</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>合理價</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>偏便宜價</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>深度買點價</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>

--- a/data/台股_體檢總表.xlsx
+++ b/data/台股_體檢總表.xlsx
@@ -3927,12 +3927,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3944,84 +3944,102 @@
         <v>90</v>
       </c>
       <c r="E27" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="F27" t="n">
-        <v>64.8</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="H27" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I27" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="J27" t="n">
-        <v>61.7</v>
+        <v>41.7</v>
       </c>
       <c r="K27" t="n">
-        <v>186</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.7</v>
+      </c>
       <c r="M27" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="N27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O27" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P27" t="n">
-        <v>30.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="R27" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="S27" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="T27" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>24</v>
+      </c>
+      <c r="W27" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.73</v>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>🟢偏便宜</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>136.7</v>
+      </c>
       <c r="AF27" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
         <v>12</v>
@@ -4036,10 +4054,10 @@
         <v>8</v>
       </c>
       <c r="AO27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -4441,12 +4459,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4458,102 +4476,84 @@
         <v>90</v>
       </c>
       <c r="E31" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>64.8</v>
       </c>
       <c r="G31" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="H31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="I31" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J31" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="K31" t="n">
-        <v>206</v>
-      </c>
-      <c r="L31" t="n">
-        <v>23.7</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P31" t="n">
-        <v>8.300000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="R31" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="S31" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="T31" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>24</v>
-      </c>
-      <c r="W31" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="X31" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0.73</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>🟢偏便宜</t>
-        </is>
-      </c>
-      <c r="AC31" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>136.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AG31" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
         <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
         <v>12</v>
@@ -4568,10 +4568,10 @@
         <v>8</v>
       </c>
       <c r="AO31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AP31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
         <v>7</v>
@@ -34221,12 +34221,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>國票金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -34236,10 +34236,10 @@
       </c>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="n">
-        <v>-16.6</v>
+        <v>4</v>
       </c>
       <c r="F264" t="n">
-        <v>4.2</v>
+        <v>37.5</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -34251,7 +34251,7 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>88.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
@@ -34263,23 +34263,23 @@
         <v>100</v>
       </c>
       <c r="P264" t="n">
-        <v>-4.1</v>
+        <v>24</v>
       </c>
       <c r="Q264" t="n">
-        <v>147.9</v>
+        <v>117.9</v>
       </c>
       <c r="R264" t="n">
-        <v>23.9</v>
+        <v>16.8</v>
       </c>
       <c r="S264" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="T264" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="V264" t="inlineStr"/>
@@ -34297,7 +34297,7 @@
       <c r="AD264" t="inlineStr"/>
       <c r="AE264" t="inlineStr"/>
       <c r="AF264" t="n">
-        <v>3.92</v>
+        <v>3.43</v>
       </c>
       <c r="AG264" t="inlineStr">
         <is>
@@ -34323,12 +34323,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -34338,10 +34338,10 @@
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="n">
-        <v>8.1</v>
+        <v>10.6</v>
       </c>
       <c r="F265" t="n">
-        <v>10.3</v>
+        <v>20.3</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -34353,7 +34353,7 @@
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>93</v>
+        <v>93.8</v>
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
@@ -34365,16 +34365,16 @@
         <v>100</v>
       </c>
       <c r="P265" t="n">
-        <v>13</v>
+        <v>7.1</v>
       </c>
       <c r="Q265" t="n">
-        <v>82.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="R265" t="n">
-        <v>20.2</v>
+        <v>17.3</v>
       </c>
       <c r="S265" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T265" t="n">
         <v>100</v>
@@ -34384,24 +34384,14 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="V265" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W265" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X265" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Y265" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Z265" t="n">
-        <v>1.97</v>
-      </c>
+      <c r="V265" t="inlineStr"/>
+      <c r="W265" t="inlineStr"/>
+      <c r="X265" t="inlineStr"/>
+      <c r="Y265" t="inlineStr"/>
+      <c r="Z265" t="inlineStr"/>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr"/>
@@ -34409,9 +34399,13 @@
       <c r="AD265" t="inlineStr"/>
       <c r="AE265" t="inlineStr"/>
       <c r="AF265" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AG265" t="inlineStr"/>
+        <v>3.55</v>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH265" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34431,12 +34425,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -34446,10 +34440,10 @@
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="n">
-        <v>-2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="F266" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -34461,7 +34455,7 @@
         <v>0</v>
       </c>
       <c r="J266" t="n">
-        <v>94.7</v>
+        <v>91.7</v>
       </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
@@ -34473,63 +34467,47 @@
         <v>100</v>
       </c>
       <c r="P266" t="n">
-        <v>8.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q266" t="n">
-        <v>17.5</v>
+        <v>227.3</v>
       </c>
       <c r="R266" t="n">
-        <v>18.5</v>
+        <v>25.1</v>
       </c>
       <c r="S266" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="T266" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V266" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W266" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X266" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Y266" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="Z266" t="n">
-        <v>2.36</v>
-      </c>
+          <t>🔴過熱</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr"/>
+      <c r="W266" t="inlineStr"/>
+      <c r="X266" t="inlineStr"/>
+      <c r="Y266" t="inlineStr"/>
+      <c r="Z266" t="inlineStr"/>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>🔴貴於合理價</t>
-        </is>
-      </c>
-      <c r="AC266" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AD266" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AE266" t="n">
-        <v>18.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr"/>
+      <c r="AD266" t="inlineStr"/>
+      <c r="AE266" t="inlineStr"/>
       <c r="AF266" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AG266" t="inlineStr"/>
+        <v>3.24</v>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH266" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34549,12 +34527,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -34564,10 +34542,10 @@
       </c>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="n">
-        <v>5.7</v>
+        <v>-9.1</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.2</v>
+        <v>47.6</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -34579,7 +34557,7 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>92</v>
+        <v>94.3</v>
       </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
@@ -34591,19 +34569,19 @@
         <v>100</v>
       </c>
       <c r="P267" t="n">
-        <v>8</v>
+        <v>-13.5</v>
       </c>
       <c r="Q267" t="n">
-        <v>22.3</v>
+        <v>28.8</v>
       </c>
       <c r="R267" t="n">
-        <v>19.8</v>
+        <v>16</v>
       </c>
       <c r="S267" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="T267" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -34620,22 +34598,12 @@
           <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>🔴貴於合理價</t>
-        </is>
-      </c>
-      <c r="AC267" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AD267" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AE267" t="n">
-        <v>29.3</v>
-      </c>
+      <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
+      <c r="AE267" t="inlineStr"/>
       <c r="AF267" t="n">
-        <v>3.75</v>
+        <v>3.03</v>
       </c>
       <c r="AG267" t="inlineStr">
         <is>
@@ -34661,12 +34629,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -34676,10 +34644,10 @@
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="F268" t="n">
-        <v>37.5</v>
+        <v>10.3</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -34691,7 +34659,7 @@
         <v>0</v>
       </c>
       <c r="J268" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
@@ -34703,16 +34671,16 @@
         <v>100</v>
       </c>
       <c r="P268" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Q268" t="n">
-        <v>117.9</v>
+        <v>82.7</v>
       </c>
       <c r="R268" t="n">
-        <v>16.8</v>
+        <v>20.2</v>
       </c>
       <c r="S268" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T268" t="n">
         <v>100</v>
@@ -34722,14 +34690,24 @@
           <t>🔴過熱</t>
         </is>
       </c>
-      <c r="V268" t="inlineStr"/>
-      <c r="W268" t="inlineStr"/>
-      <c r="X268" t="inlineStr"/>
-      <c r="Y268" t="inlineStr"/>
-      <c r="Z268" t="inlineStr"/>
+      <c r="V268" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X268" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>1.97</v>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="AB268" t="inlineStr"/>
@@ -34737,13 +34715,9 @@
       <c r="AD268" t="inlineStr"/>
       <c r="AE268" t="inlineStr"/>
       <c r="AF268" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.27</v>
+      </c>
+      <c r="AG268" t="inlineStr"/>
       <c r="AH268" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34763,12 +34737,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -34778,10 +34752,10 @@
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="n">
-        <v>-1.2</v>
+        <v>5.7</v>
       </c>
       <c r="F269" t="n">
-        <v>14.5</v>
+        <v>-0.2</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -34793,7 +34767,7 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>91.7</v>
+        <v>92</v>
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
@@ -34805,19 +34779,19 @@
         <v>100</v>
       </c>
       <c r="P269" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="Q269" t="n">
-        <v>227.3</v>
+        <v>22.3</v>
       </c>
       <c r="R269" t="n">
-        <v>25.1</v>
+        <v>19.8</v>
       </c>
       <c r="S269" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="T269" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -34834,12 +34808,22 @@
           <t>⏸ 循環(看PBR)</t>
         </is>
       </c>
-      <c r="AB269" t="inlineStr"/>
-      <c r="AC269" t="inlineStr"/>
-      <c r="AD269" t="inlineStr"/>
-      <c r="AE269" t="inlineStr"/>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>🔴貴於合理價</t>
+        </is>
+      </c>
+      <c r="AC269" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>29.3</v>
+      </c>
       <c r="AF269" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AG269" t="inlineStr">
         <is>
@@ -34865,12 +34849,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -34880,10 +34864,10 @@
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="n">
-        <v>-7.1</v>
+        <v>-2.6</v>
       </c>
       <c r="F270" t="n">
-        <v>24.1</v>
+        <v>7.8</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -34895,7 +34879,7 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>91.2</v>
+        <v>94.7</v>
       </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
@@ -34907,47 +34891,63 @@
         <v>100</v>
       </c>
       <c r="P270" t="n">
-        <v>-24</v>
+        <v>8.1</v>
       </c>
       <c r="Q270" t="n">
-        <v>-172.7</v>
+        <v>17.5</v>
       </c>
       <c r="R270" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="S270" t="n">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="T270" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
-      <c r="X270" t="inlineStr"/>
-      <c r="Y270" t="inlineStr"/>
-      <c r="Z270" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V270" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X270" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>2.36</v>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr"/>
-      <c r="AC270" t="inlineStr"/>
-      <c r="AD270" t="inlineStr"/>
-      <c r="AE270" t="inlineStr"/>
+          <t>🟠未來偏貴</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>🔴貴於合理價</t>
+        </is>
+      </c>
+      <c r="AC270" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>18.7</v>
+      </c>
       <c r="AF270" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>4.18</v>
+      </c>
+      <c r="AG270" t="inlineStr"/>
       <c r="AH270" t="inlineStr">
         <is>
           <t>金融股:口徑不適用,不評分</t>
@@ -34967,12 +34967,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>國票金</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -34982,10 +34982,10 @@
       </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="n">
-        <v>-9.5</v>
+        <v>-16.6</v>
       </c>
       <c r="F271" t="n">
-        <v>32.1</v>
+        <v>4.2</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -34997,7 +34997,7 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>92.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
@@ -35009,23 +35009,23 @@
         <v>100</v>
       </c>
       <c r="P271" t="n">
-        <v>-5.9</v>
+        <v>-4.1</v>
       </c>
       <c r="Q271" t="n">
-        <v>-300.3</v>
+        <v>147.9</v>
       </c>
       <c r="R271" t="n">
-        <v>16.6</v>
+        <v>23.9</v>
       </c>
       <c r="S271" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="T271" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="V271" t="inlineStr"/>
@@ -35043,7 +35043,7 @@
       <c r="AD271" t="inlineStr"/>
       <c r="AE271" t="inlineStr"/>
       <c r="AF271" t="n">
-        <v>3.08</v>
+        <v>3.92</v>
       </c>
       <c r="AG271" t="inlineStr">
         <is>
@@ -35069,12 +35069,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -35084,10 +35084,10 @@
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="n">
-        <v>10.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F272" t="n">
-        <v>20.3</v>
+        <v>22.6</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -35099,7 +35099,7 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
@@ -35111,23 +35111,23 @@
         <v>100</v>
       </c>
       <c r="P272" t="n">
-        <v>7.1</v>
+        <v>12.2</v>
       </c>
       <c r="Q272" t="n">
-        <v>76.09999999999999</v>
+        <v>24.8</v>
       </c>
       <c r="R272" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="S272" t="n">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="T272" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>🔴過熱</t>
+          <t>🟡合理</t>
         </is>
       </c>
       <c r="V272" t="inlineStr"/>
@@ -35145,7 +35145,7 @@
       <c r="AD272" t="inlineStr"/>
       <c r="AE272" t="inlineStr"/>
       <c r="AF272" t="n">
-        <v>3.55</v>
+        <v>3.91</v>
       </c>
       <c r="AG272" t="inlineStr">
         <is>
@@ -35171,12 +35171,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -35186,10 +35186,10 @@
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="n">
-        <v>8.300000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="F273" t="n">
-        <v>22.6</v>
+        <v>32.1</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -35201,7 +35201,7 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>93.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
@@ -35213,23 +35213,23 @@
         <v>100</v>
       </c>
       <c r="P273" t="n">
-        <v>12.2</v>
+        <v>-5.9</v>
       </c>
       <c r="Q273" t="n">
-        <v>24.8</v>
+        <v>-300.3</v>
       </c>
       <c r="R273" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="S273" t="n">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="T273" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>🟡合理</t>
+          <t>🔴過熱</t>
         </is>
       </c>
       <c r="V273" t="inlineStr"/>
@@ -35247,7 +35247,7 @@
       <c r="AD273" t="inlineStr"/>
       <c r="AE273" t="inlineStr"/>
       <c r="AF273" t="n">
-        <v>3.91</v>
+        <v>3.08</v>
       </c>
       <c r="AG273" t="inlineStr">
         <is>
@@ -35273,12 +35273,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -35288,10 +35288,10 @@
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
       <c r="F274" t="n">
-        <v>47.6</v>
+        <v>24.1</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -35303,7 +35303,7 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>94.3</v>
+        <v>91.2</v>
       </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
@@ -35315,16 +35315,16 @@
         <v>100</v>
       </c>
       <c r="P274" t="n">
-        <v>-13.5</v>
+        <v>-24</v>
       </c>
       <c r="Q274" t="n">
-        <v>28.8</v>
+        <v>-172.7</v>
       </c>
       <c r="R274" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="S274" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="T274" t="n">
         <v>100</v>
@@ -35349,7 +35349,7 @@
       <c r="AD274" t="inlineStr"/>
       <c r="AE274" t="inlineStr"/>
       <c r="AF274" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="AG274" t="inlineStr">
         <is>
@@ -38081,12 +38081,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -38098,107 +38098,89 @@
         <v>90</v>
       </c>
       <c r="E27" t="n">
-        <v>46.8</v>
+        <v>31.4</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>64.8</v>
       </c>
       <c r="G27" t="n">
-        <v>20.7</v>
+        <v>33.3</v>
       </c>
       <c r="H27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="I27" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J27" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="K27" t="n">
-        <v>206</v>
-      </c>
-      <c r="L27" t="n">
-        <v>23.7</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P27" t="n">
-        <v>8.300000000000001</v>
+        <v>30.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>14.9</v>
+        <v>58.3</v>
       </c>
       <c r="R27" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="S27" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="T27" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>🟡合理</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>24</v>
-      </c>
-      <c r="W27" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="X27" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.73</v>
-      </c>
+          <t>🟠偏貴</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>🟢偏便宜</t>
-        </is>
-      </c>
-      <c r="AC27" t="n">
-        <v>203.7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>136.7</v>
-      </c>
+          <t>⏸ 循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AG27" t="inlineStr"/>
+        <v>2.24</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -38210,78 +38192,96 @@
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>31.4</v>
+        <v>46.8</v>
       </c>
       <c r="F28" t="n">
-        <v>64.8</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>33.3</v>
+        <v>20.7</v>
       </c>
       <c r="H28" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="I28" t="n">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="J28" t="n">
-        <v>61.7</v>
+        <v>41.7</v>
       </c>
       <c r="K28" t="n">
-        <v>186</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.7</v>
+      </c>
       <c r="M28" t="n">
-        <v>0.92</v>
+        <v>1.16</v>
       </c>
       <c r="N28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O28" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P28" t="n">
-        <v>30.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>58.3</v>
+        <v>14.9</v>
       </c>
       <c r="R28" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="S28" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="T28" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>🟠偏貴</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>🟡合理</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>24</v>
+      </c>
+      <c r="W28" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.73</v>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>⏸ 循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>🟢偏便宜</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>136.7</v>
+      </c>
       <c r="AF28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -53607,64 +53607,64 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E114" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="F114" t="n">
-        <v>35.8</v>
+        <v>32.7</v>
       </c>
       <c r="G114" t="n">
-        <v>24.3</v>
+        <v>14.1</v>
       </c>
       <c r="H114" t="n">
-        <v>20</v>
+        <v>18.8</v>
       </c>
       <c r="I114" t="n">
-        <v>10.7</v>
+        <v>5.8</v>
       </c>
       <c r="J114" t="n">
-        <v>56</v>
+        <v>58.8</v>
       </c>
       <c r="K114" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>-1.89</v>
+        <v>1.43</v>
       </c>
       <c r="N114" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="O114" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="P114" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q114" t="n">
-        <v>64.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="R114" t="n">
-        <v>49.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="S114" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T114" t="n">
         <v>99</v>
@@ -53689,18 +53689,14 @@
       <c r="AD114" t="inlineStr"/>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="n">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>含金量-1.9差、毛利壓歷史低檔</t>
-        </is>
-      </c>
+      <c r="AH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -53803,64 +53799,64 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E116" t="n">
-        <v>18</v>
+        <v>-34.5</v>
       </c>
       <c r="F116" t="n">
-        <v>25.3</v>
+        <v>-42.1</v>
       </c>
       <c r="G116" t="n">
-        <v>18.1</v>
+        <v>6.5</v>
       </c>
       <c r="H116" t="n">
-        <v>15.7</v>
+        <v>17.4</v>
       </c>
       <c r="I116" t="n">
-        <v>11.1</v>
+        <v>4.9</v>
       </c>
       <c r="J116" t="n">
-        <v>38.6</v>
+        <v>24.9</v>
       </c>
       <c r="K116" t="n">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="N116" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="O116" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="P116" t="n">
-        <v>7.8</v>
+        <v>-6.3</v>
       </c>
       <c r="Q116" t="n">
-        <v>17.8</v>
+        <v>35.8</v>
       </c>
       <c r="R116" t="n">
-        <v>69.5</v>
+        <v>192.6</v>
       </c>
       <c r="S116" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="T116" t="n">
         <v>99</v>
@@ -53885,14 +53881,18 @@
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="n">
-        <v>0.7</v>
+        <v>0.22</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>EPS連年衰退、ROE6低、營收5年萎縮-6%</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -54493,64 +54493,64 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="E123" t="n">
-        <v>-34.5</v>
+        <v>18</v>
       </c>
       <c r="F123" t="n">
-        <v>-42.1</v>
+        <v>25.3</v>
       </c>
       <c r="G123" t="n">
-        <v>6.5</v>
+        <v>18.1</v>
       </c>
       <c r="H123" t="n">
-        <v>17.4</v>
+        <v>15.7</v>
       </c>
       <c r="I123" t="n">
-        <v>4.9</v>
+        <v>11.1</v>
       </c>
       <c r="J123" t="n">
-        <v>24.9</v>
+        <v>38.6</v>
       </c>
       <c r="K123" t="n">
-        <v>318</v>
+        <v>179</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="N123" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="O123" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P123" t="n">
-        <v>-6.3</v>
+        <v>7.8</v>
       </c>
       <c r="Q123" t="n">
-        <v>35.8</v>
+        <v>17.8</v>
       </c>
       <c r="R123" t="n">
-        <v>192.6</v>
+        <v>69.5</v>
       </c>
       <c r="S123" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="T123" t="n">
         <v>99</v>
@@ -54575,18 +54575,14 @@
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="n">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>EPS連年衰退、ROE6低、營收5年萎縮-6%</t>
-        </is>
-      </c>
+      <c r="AH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -54969,64 +54965,64 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E128" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="F128" t="n">
-        <v>32.7</v>
+        <v>35.8</v>
       </c>
       <c r="G128" t="n">
-        <v>14.1</v>
+        <v>24.3</v>
       </c>
       <c r="H128" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="I128" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="J128" t="n">
-        <v>58.8</v>
+        <v>56</v>
       </c>
       <c r="K128" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
-        <v>1.43</v>
+        <v>-1.89</v>
       </c>
       <c r="N128" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="O128" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="P128" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q128" t="n">
-        <v>74.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="R128" t="n">
-        <v>83.40000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="S128" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T128" t="n">
         <v>99</v>
@@ -55051,14 +55047,18 @@
       <c r="AD128" t="inlineStr"/>
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="n">
-        <v>0.87</v>
+        <v>1.23</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>含金量-1.9差、毛利壓歷史低檔</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -55559,62 +55559,64 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E134" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
+        <v>-14.6</v>
+      </c>
+      <c r="F134" t="n">
+        <v>12.1</v>
+      </c>
       <c r="G134" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="H134" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="I134" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="J134" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K134" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
-        <v>1.73</v>
+        <v>0.99</v>
       </c>
       <c r="N134" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O134" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="P134" t="n">
-        <v>4.5</v>
+        <v>-5.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>49.9</v>
+        <v>21.3</v>
       </c>
       <c r="R134" t="n">
-        <v>165.8</v>
+        <v>115.6</v>
       </c>
       <c r="S134" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="T134" t="n">
         <v>100</v>
@@ -55639,7 +55641,7 @@
       <c r="AD134" t="inlineStr"/>
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="n">
-        <v>0.18</v>
+        <v>0.65</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -55648,7 +55650,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>EPS資料不足</t>
+          <t>EPS單期衰退、營收5年萎縮-5%</t>
         </is>
       </c>
     </row>
@@ -55949,64 +55951,62 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E138" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="F138" t="n">
-        <v>12.1</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>12.4</v>
+        <v>10.7</v>
       </c>
       <c r="H138" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I138" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J138" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K138" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
-        <v>0.99</v>
+        <v>1.73</v>
       </c>
       <c r="N138" t="n">
+        <v>77</v>
+      </c>
+      <c r="O138" t="n">
         <v>55</v>
       </c>
-      <c r="O138" t="n">
-        <v>73</v>
-      </c>
       <c r="P138" t="n">
-        <v>-5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q138" t="n">
-        <v>21.3</v>
+        <v>49.9</v>
       </c>
       <c r="R138" t="n">
-        <v>115.6</v>
+        <v>165.8</v>
       </c>
       <c r="S138" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="T138" t="n">
         <v>100</v>
@@ -56031,7 +56031,7 @@
       <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="n">
-        <v>0.65</v>
+        <v>0.18</v>
       </c>
       <c r="AG138" t="inlineStr">
         <is>
@@ -56040,71 +56040,71 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>EPS單期衰退、營收5年萎縮-5%</t>
+          <t>EPS資料不足</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E139" t="n">
-        <v>-16.5</v>
+        <v>-12.8</v>
       </c>
       <c r="F139" t="n">
-        <v>-25.4</v>
+        <v>-19.8</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3</v>
+        <v>15.5</v>
       </c>
       <c r="H139" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="I139" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="J139" t="n">
-        <v>56.2</v>
+        <v>57.9</v>
       </c>
       <c r="K139" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="N139" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="O139" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="P139" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q139" t="n">
-        <v>32.4</v>
+        <v>47.5</v>
       </c>
       <c r="R139" t="n">
-        <v>142.3</v>
+        <v>53.2</v>
       </c>
       <c r="S139" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T139" t="n">
         <v>100</v>
@@ -56129,7 +56129,7 @@
       <c r="AD139" t="inlineStr"/>
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG139" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️ROE滑落(10&lt;5年均16×67%)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
@@ -56243,64 +56243,64 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E141" t="n">
-        <v>-12.8</v>
+        <v>-16.5</v>
       </c>
       <c r="F141" t="n">
-        <v>-19.8</v>
+        <v>-25.4</v>
       </c>
       <c r="G141" t="n">
-        <v>15.5</v>
+        <v>10.3</v>
       </c>
       <c r="H141" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
       <c r="I141" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="J141" t="n">
-        <v>57.9</v>
+        <v>56.2</v>
       </c>
       <c r="K141" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="N141" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="O141" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="P141" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q141" t="n">
-        <v>47.5</v>
+        <v>32.4</v>
       </c>
       <c r="R141" t="n">
-        <v>53.2</v>
+        <v>142.3</v>
       </c>
       <c r="S141" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="T141" t="n">
         <v>100</v>
@@ -56325,7 +56325,7 @@
       <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
@@ -56334,7 +56334,7 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)、⚠️ROE滑落(10&lt;5年均16×67%)</t>
         </is>
       </c>
     </row>
@@ -56831,64 +56831,64 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>茂達</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3</v>
+        <v>-5.5</v>
       </c>
       <c r="F147" t="n">
-        <v>36.5</v>
+        <v>-5.4</v>
       </c>
       <c r="G147" t="n">
-        <v>28.8</v>
+        <v>20.2</v>
       </c>
       <c r="H147" t="n">
-        <v>25.6</v>
+        <v>24.1</v>
       </c>
       <c r="I147" t="n">
-        <v>17.4</v>
+        <v>11.2</v>
       </c>
       <c r="J147" t="n">
-        <v>39.7</v>
+        <v>44.6</v>
       </c>
       <c r="K147" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="n">
-        <v>1.21</v>
+        <v>0.92</v>
       </c>
       <c r="N147" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O147" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="P147" t="n">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q147" t="n">
-        <v>15.4</v>
+        <v>81.7</v>
       </c>
       <c r="R147" t="n">
-        <v>27.9</v>
+        <v>25.9</v>
       </c>
       <c r="S147" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="T147" t="n">
         <v>100</v>
@@ -56913,7 +56913,7 @@
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
@@ -56922,71 +56922,71 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>茂達</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E148" t="n">
-        <v>-5.5</v>
+        <v>0.3</v>
       </c>
       <c r="F148" t="n">
-        <v>-5.4</v>
+        <v>36.5</v>
       </c>
       <c r="G148" t="n">
-        <v>20.2</v>
+        <v>28.8</v>
       </c>
       <c r="H148" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="I148" t="n">
-        <v>11.2</v>
+        <v>17.4</v>
       </c>
       <c r="J148" t="n">
-        <v>44.6</v>
+        <v>39.7</v>
       </c>
       <c r="K148" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="N148" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="O148" t="n">
+        <v>77</v>
+      </c>
+      <c r="P148" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="R148" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S148" t="n">
         <v>91</v>
-      </c>
-      <c r="P148" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="R148" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="S148" t="n">
-        <v>100</v>
       </c>
       <c r="T148" t="n">
         <v>100</v>
@@ -57011,7 +57011,7 @@
       <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="AG148" t="inlineStr">
         <is>
@@ -57020,71 +57020,71 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>EPS連年衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+          <t>EPS遠落後營收(稀釋/毛利漏)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="E149" t="n">
-        <v>-3.4</v>
+        <v>47.6</v>
       </c>
       <c r="F149" t="n">
-        <v>27</v>
+        <v>90.7</v>
       </c>
       <c r="G149" t="n">
-        <v>31.7</v>
+        <v>34.3</v>
       </c>
       <c r="H149" t="n">
-        <v>33.9</v>
+        <v>23</v>
       </c>
       <c r="I149" t="n">
-        <v>10</v>
+        <v>27.4</v>
       </c>
       <c r="J149" t="n">
-        <v>68.40000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="K149" t="n">
-        <v>115</v>
+        <v>547</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="N149" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="O149" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="P149" t="n">
-        <v>3.8</v>
+        <v>28.8</v>
       </c>
       <c r="Q149" t="n">
-        <v>21.9</v>
+        <v>172.1</v>
       </c>
       <c r="R149" t="n">
-        <v>32.2</v>
+        <v>66.5</v>
       </c>
       <c r="S149" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T149" t="n">
         <v>100</v>
@@ -57109,80 +57109,76 @@
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="n">
-        <v>2.78</v>
+        <v>0.68</v>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
-        </is>
-      </c>
+      <c r="AH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E150" t="n">
-        <v>47.6</v>
+        <v>-3.4</v>
       </c>
       <c r="F150" t="n">
-        <v>90.7</v>
+        <v>27</v>
       </c>
       <c r="G150" t="n">
-        <v>34.3</v>
+        <v>31.7</v>
       </c>
       <c r="H150" t="n">
-        <v>23</v>
+        <v>33.9</v>
       </c>
       <c r="I150" t="n">
-        <v>27.4</v>
+        <v>10</v>
       </c>
       <c r="J150" t="n">
-        <v>20.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K150" t="n">
-        <v>547</v>
+        <v>115</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="N150" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="O150" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="P150" t="n">
-        <v>28.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q150" t="n">
-        <v>172.1</v>
+        <v>21.9</v>
       </c>
       <c r="R150" t="n">
-        <v>66.5</v>
+        <v>32.2</v>
       </c>
       <c r="S150" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T150" t="n">
         <v>100</v>
@@ -57207,14 +57203,18 @@
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="n">
-        <v>0.68</v>
+        <v>2.78</v>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="AH150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>EPS單期衰退、EPS遠落後營收(稀釋/毛利漏)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
